--- a/case_studies/base_case_10_dd/2050/technologies.xlsx
+++ b/case_studies/base_case_10_dd/2050/technologies.xlsx
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -691,52 +691,52 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>55.45</v>
+        <v>115.62</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>353.04</v>
+        <v>471.63</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>24.96</v>
+        <v>20.66</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>11.38</v>
+        <v>946.41</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>11.38</v>
+        <v>946.41</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>114.38</v>
+        <v>231.24</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>163.1</v>
+        <v>257.06</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0</v>
+        <v>36.8</v>
       </c>
       <c r="S2" s="3" t="n">
         <v>22.37</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>1.92</v>
+        <v>159.94</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>39.34</v>
+        <v>49.16</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>240.36</v>
+        <v>239.66</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>0</v>
+        <v>684.16</v>
       </c>
       <c r="Y2" s="3" t="n">
         <v>0</v>
@@ -770,19 +770,19 @@
         <v>5.21</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0</v>
+        <v>1247.24</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0</v>
+        <v>45.66</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>3.55</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0</v>
+        <v>35.39</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>0</v>
+        <v>32.33</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="U3" s="5" t="n">
         <v>0</v>
@@ -836,10 +836,10 @@
         <v>0</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>0</v>
+        <v>44.45</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -870,73 +870,73 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>39.95</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>102.11</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>168.32</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>143.64</v>
+        <v>661.12</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>111.73</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0</v>
+        <v>1369.36</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0</v>
+        <v>1369.36</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>93.92</v>
+        <v>606.09</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>156.42</v>
+        <v>641.36</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>143.41</v>
+        <v>348.71</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>43.32</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0</v>
+        <v>231.42</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>0</v>
+        <v>11.05</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>144.41</v>
+        <v>345.71</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>30.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>27.91</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -967,46 +967,46 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>216.89</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>38.39</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>28.15</v>
+        <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>257.29</v>
+        <v>405.25</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>52.56</v>
+        <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>23.95</v>
+        <v>745.4</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>23.95</v>
+        <v>745.4</v>
       </c>
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>39.94</v>
+        <v>129.9</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>39.94</v>
+        <v>129.9</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>4.04</v>
+        <v>125.97</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
@@ -1024,16 +1024,16 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>189.3</v>
+        <v>182.66</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>643.22</v>
+        <v>263.59</v>
       </c>
       <c r="Y5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>0</v>
+        <v>204.22</v>
       </c>
       <c r="AA5" s="5" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>51.37</v>
+        <v>61.1</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>156.18</v>
+        <v>221.12</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1091,28 +1091,28 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0</v>
+        <v>565.33</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0</v>
+        <v>565.33</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>179.81</v>
+        <v>204.43</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>179.81</v>
+        <v>204.43</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>99.73</v>
+        <v>106.41</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
@@ -1121,10 +1121,10 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>99.73</v>
+        <v>106.41</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>361.56</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>0</v>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>19.67</v>
+        <v>48.52</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>3.11</v>
+        <v>59.3</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
@@ -1197,28 +1197,28 @@
         <v>0</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>24</v>
+        <v>97.03</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>0</v>
+        <v>19.82</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>0</v>
+        <v>15.67</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>19.67</v>
+        <v>48.52</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>0</v>
+        <v>19.43</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>108.4</v>
+        <v>128.76</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>158.68</v>
+        <v>287.46</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1285,37 +1285,37 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0</v>
+        <v>136.33</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0</v>
+        <v>136.33</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>166.26</v>
+        <v>342.61</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>219.24</v>
+        <v>427.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0</v>
+        <v>129.95</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>35.73</v>
+        <v>73.62</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>42.85</v>
+        <v>128.76</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.88</v>
+        <v>2.59</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>44.74</v>
+        <v>129.51</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>136.33</v>

--- a/case_studies/base_case_10_dd/2050/technologies.xlsx
+++ b/case_studies/base_case_10_dd/2050/technologies.xlsx
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.57</v>
+        <v>4.86</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -691,13 +691,13 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>115.62</v>
+        <v>114.1</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>471.63</v>
+        <v>454.17</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>20.66</v>
+        <v>21.09</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -706,16 +706,16 @@
         <v>946.41</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>946.41</v>
+        <v>983.99</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>231.24</v>
+        <v>228.2</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>257.06</v>
+        <v>273.76</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>36.8</v>
@@ -733,10 +733,10 @@
         <v>49.16</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>239.66</v>
+        <v>237.02</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>684.16</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
         <v>0</v>
@@ -770,7 +770,7 @@
         <v>5.21</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1247.24</v>
+        <v>1534.49</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>45.66</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>6.62</v>
+        <v>14.59</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>8.08</v>
@@ -794,7 +794,7 @@
         <v>35.39</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>32.33</v>
+        <v>35.22</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>44.45</v>
+        <v>48.42</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>102.11</v>
+        <v>94.33</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>7.07</v>
@@ -885,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>168.32</v>
+        <v>176.52</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>661.12</v>
+        <v>663.88</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>111.73</v>
+        <v>54.33</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
@@ -900,37 +900,37 @@
         <v>1369.36</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1369.36</v>
+        <v>1502.3</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>606.09</v>
+        <v>607.9400000000001</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>641.36</v>
+        <v>643.22</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>348.71</v>
+        <v>351.55</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>43.32</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>231.42</v>
+        <v>260.55</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>11.05</v>
+        <v>14.73</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>345.71</v>
+        <v>348.55</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0</v>
+        <v>611.7</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
@@ -964,28 +964,28 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0</v>
+        <v>22.53</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>216.89</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.83</v>
+        <v>9.06</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>108.43</v>
+        <v>109.13</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>405.25</v>
+        <v>425.52</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>148.52</v>
@@ -997,16 +997,16 @@
         <v>745.4</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>745.4</v>
+        <v>746.15</v>
       </c>
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>129.9</v>
+        <v>131.18</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>129.9</v>
+        <v>131.18</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>182.66</v>
+        <v>185.74</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>263.59</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="5" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5.85</v>
+        <v>6.58</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>61.1</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>221.12</v>
@@ -1124,7 +1124,7 @@
         <v>106.41</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0</v>
+        <v>361.56</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.82</v>
+        <v>19.57</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.67</v>
+        <v>15.8</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1218,7 +1218,7 @@
         <v>1.43</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.43</v>
+        <v>19.18</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.01</v>
+        <v>3.81</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>

--- a/case_studies/base_case_10_dd/2050/technologies.xlsx
+++ b/case_studies/base_case_10_dd/2050/technologies.xlsx
@@ -770,7 +770,7 @@
         <v>5.21</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>427.24</v>
+        <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>45.66</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>8.08</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>44.46</v>
+        <v>44.45</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
@@ -985,13 +985,13 @@
         <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>417.43</v>
+        <v>416.54</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>95.23999999999999</v>
+        <v>100.28</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>745.4</v>
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>368.71</v>
+        <v>333.62</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>387.66</v>
+        <v>352.57</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>12.77</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>203.67</v>
+        <v>208.71</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
@@ -1024,13 +1024,13 @@
         <v>0.55</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>723.45</v>
+        <v>719.79</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>13.7</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>54401.28</v>
+        <v>53515.35</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>204.22</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>288.69</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>7.66</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>81.45999999999999</v>
